--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3022"/>
+  <dimension ref="A1:E3023"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82010,6 +82010,33 @@
         </is>
       </c>
     </row>
+    <row r="3023">
+      <c r="A3023" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B3023" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3023" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3023" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E3023" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3023"/>
+  <dimension ref="A1:E3024"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82037,6 +82037,33 @@
         </is>
       </c>
     </row>
+    <row r="3024">
+      <c r="A3024" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B3024" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3024" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D3024" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3024" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3024"/>
+  <dimension ref="A1:E3025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82064,6 +82064,33 @@
         </is>
       </c>
     </row>
+    <row r="3025">
+      <c r="A3025" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B3025" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3025" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3025" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="E3025" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3025"/>
+  <dimension ref="A1:E3026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82091,6 +82091,33 @@
         </is>
       </c>
     </row>
+    <row r="3026">
+      <c r="A3026" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B3026" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3026" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D3026" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E3026" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3026"/>
+  <dimension ref="A1:E3027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82118,6 +82118,33 @@
         </is>
       </c>
     </row>
+    <row r="3027">
+      <c r="A3027" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B3027" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3027" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3027" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E3027" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3027"/>
+  <dimension ref="A1:E3028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82145,6 +82145,33 @@
         </is>
       </c>
     </row>
+    <row r="3028">
+      <c r="A3028" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B3028" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3028" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D3028" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3028" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3028"/>
+  <dimension ref="A1:E3029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82172,6 +82172,33 @@
         </is>
       </c>
     </row>
+    <row r="3029">
+      <c r="A3029" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B3029" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3029" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3029" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3029" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3029"/>
+  <dimension ref="A1:E3030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82199,6 +82199,33 @@
         </is>
       </c>
     </row>
+    <row r="3030">
+      <c r="A3030" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3030" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3030" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D3030" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3030" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3030"/>
+  <dimension ref="A1:E3034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82202,27 +82202,135 @@
     <row r="3030">
       <c r="A3030" t="inlineStr">
         <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B3030" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3030" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3030" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E3030" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+    </row>
+    <row r="3031">
+      <c r="A3031" t="inlineStr">
+        <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="B3030" t="inlineStr">
+      <c r="B3031" t="inlineStr">
         <is>
           <t>Anguila 10AM</t>
         </is>
       </c>
-      <c r="C3030" t="inlineStr">
+      <c r="C3031" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D3030" t="inlineStr">
+      <c r="D3031" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E3030" t="inlineStr">
+      <c r="E3031" t="inlineStr">
         <is>
           <t>61</t>
+        </is>
+      </c>
+    </row>
+    <row r="3032">
+      <c r="A3032" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3032" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3032" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D3032" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E3032" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3033">
+      <c r="A3033" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3033" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3033" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3033" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3033" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="3034">
+      <c r="A3034" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3034" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3034" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3034" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E3034" t="inlineStr">
+        <is>
+          <t>69</t>
         </is>
       </c>
     </row>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3033"/>
+  <dimension ref="A1:E3034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82307,6 +82307,33 @@
         </is>
       </c>
     </row>
+    <row r="3034">
+      <c r="A3034" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B3034" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3034" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3034" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E3034" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3034"/>
+  <dimension ref="A1:E3035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82334,6 +82334,33 @@
         </is>
       </c>
     </row>
+    <row r="3035">
+      <c r="A3035" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B3035" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3035" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3035" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3035" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3035"/>
+  <dimension ref="A1:E3036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82361,6 +82361,33 @@
         </is>
       </c>
     </row>
+    <row r="3036">
+      <c r="A3036" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B3036" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3036" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3036" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3036" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3036"/>
+  <dimension ref="A1:E3037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82388,6 +82388,33 @@
         </is>
       </c>
     </row>
+    <row r="3037">
+      <c r="A3037" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B3037" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3037" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D3037" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3037" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3037"/>
+  <dimension ref="A1:E3038"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82415,6 +82415,33 @@
         </is>
       </c>
     </row>
+    <row r="3038">
+      <c r="A3038" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B3038" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3038" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3038" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3038" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3038"/>
+  <dimension ref="A1:E3039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82442,6 +82442,33 @@
         </is>
       </c>
     </row>
+    <row r="3039">
+      <c r="A3039" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B3039" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3039" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D3039" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3039" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3039"/>
+  <dimension ref="A1:E3040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82469,6 +82469,33 @@
         </is>
       </c>
     </row>
+    <row r="3040">
+      <c r="A3040" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B3040" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3040" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D3040" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3040" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3040"/>
+  <dimension ref="A1:E3041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82496,6 +82496,33 @@
         </is>
       </c>
     </row>
+    <row r="3041">
+      <c r="A3041" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B3041" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3041" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3041" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E3041" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3041"/>
+  <dimension ref="A1:E3042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82523,6 +82523,33 @@
         </is>
       </c>
     </row>
+    <row r="3042">
+      <c r="A3042" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B3042" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3042" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D3042" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3042" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3042"/>
+  <dimension ref="A1:E3043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82550,6 +82550,33 @@
         </is>
       </c>
     </row>
+    <row r="3043">
+      <c r="A3043" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B3043" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3043" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D3043" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3043" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3043"/>
+  <dimension ref="A1:E3044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82577,6 +82577,33 @@
         </is>
       </c>
     </row>
+    <row r="3044">
+      <c r="A3044" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B3044" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3044" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3044" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3044" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3044"/>
+  <dimension ref="A1:E3045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82604,6 +82604,33 @@
         </is>
       </c>
     </row>
+    <row r="3045">
+      <c r="A3045" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B3045" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3045" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D3045" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3045" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3045"/>
+  <dimension ref="A1:E3046"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82631,6 +82631,33 @@
         </is>
       </c>
     </row>
+    <row r="3046">
+      <c r="A3046" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B3046" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3046" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3046" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3046" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3046"/>
+  <dimension ref="A1:E3047"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82658,6 +82658,33 @@
         </is>
       </c>
     </row>
+    <row r="3047">
+      <c r="A3047" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B3047" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3047" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D3047" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E3047" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3047"/>
+  <dimension ref="A1:E3048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82685,6 +82685,33 @@
         </is>
       </c>
     </row>
+    <row r="3048">
+      <c r="A3048" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B3048" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3048" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D3048" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E3048" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3048"/>
+  <dimension ref="A1:E3049"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82712,6 +82712,33 @@
         </is>
       </c>
     </row>
+    <row r="3049">
+      <c r="A3049" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B3049" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3049" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D3049" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E3049" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3049"/>
+  <dimension ref="A1:E3050"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82739,6 +82739,33 @@
         </is>
       </c>
     </row>
+    <row r="3050">
+      <c r="A3050" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B3050" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3050" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D3050" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3050" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3050"/>
+  <dimension ref="A1:E3051"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82766,6 +82766,33 @@
         </is>
       </c>
     </row>
+    <row r="3051">
+      <c r="A3051" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B3051" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3051" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D3051" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E3051" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3051"/>
+  <dimension ref="A1:E3052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82793,6 +82793,33 @@
         </is>
       </c>
     </row>
+    <row r="3052">
+      <c r="A3052" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B3052" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3052" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3052" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3052" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3052"/>
+  <dimension ref="A1:E3053"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82820,6 +82820,33 @@
         </is>
       </c>
     </row>
+    <row r="3053">
+      <c r="A3053" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B3053" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3053" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3053" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E3053" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3053"/>
+  <dimension ref="A1:E3054"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82847,6 +82847,33 @@
         </is>
       </c>
     </row>
+    <row r="3054">
+      <c r="A3054" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B3054" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3054" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3054" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3054" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3054"/>
+  <dimension ref="A1:E3055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82874,6 +82874,33 @@
         </is>
       </c>
     </row>
+    <row r="3055">
+      <c r="A3055" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B3055" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3055" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D3055" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3055" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3055"/>
+  <dimension ref="A1:E3056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82901,6 +82901,33 @@
         </is>
       </c>
     </row>
+    <row r="3056">
+      <c r="A3056" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B3056" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3056" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D3056" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3056" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3056"/>
+  <dimension ref="A1:E3057"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82928,6 +82928,33 @@
         </is>
       </c>
     </row>
+    <row r="3057">
+      <c r="A3057" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B3057" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3057" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D3057" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3057" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3057"/>
+  <dimension ref="A1:E3059"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82955,6 +82955,60 @@
         </is>
       </c>
     </row>
+    <row r="3058">
+      <c r="A3058" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B3058" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3058" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D3058" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3058" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="3059">
+      <c r="A3059" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B3059" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3059" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D3059" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3059" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3059"/>
+  <dimension ref="A1:E3060"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83009,6 +83009,33 @@
         </is>
       </c>
     </row>
+    <row r="3060">
+      <c r="A3060" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B3060" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3060" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D3060" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3060" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3060"/>
+  <dimension ref="A1:E3061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83036,6 +83036,33 @@
         </is>
       </c>
     </row>
+    <row r="3061">
+      <c r="A3061" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B3061" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3061" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D3061" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E3061" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3061"/>
+  <dimension ref="A1:E3062"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83063,6 +83063,33 @@
         </is>
       </c>
     </row>
+    <row r="3062">
+      <c r="A3062" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B3062" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3062" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D3062" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3062" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3062"/>
+  <dimension ref="A1:E3063"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83090,6 +83090,33 @@
         </is>
       </c>
     </row>
+    <row r="3063">
+      <c r="A3063" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B3063" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3063" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D3063" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3063" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3063"/>
+  <dimension ref="A1:E3064"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83117,6 +83117,33 @@
         </is>
       </c>
     </row>
+    <row r="3064">
+      <c r="A3064" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B3064" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3064" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D3064" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E3064" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3064"/>
+  <dimension ref="A1:E3065"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83144,6 +83144,33 @@
         </is>
       </c>
     </row>
+    <row r="3065">
+      <c r="A3065" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B3065" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3065" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D3065" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3065" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3065"/>
+  <dimension ref="A1:E3066"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83171,6 +83171,33 @@
         </is>
       </c>
     </row>
+    <row r="3066">
+      <c r="A3066" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B3066" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3066" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3066" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3066" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3066"/>
+  <dimension ref="A1:E3067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83198,6 +83198,33 @@
         </is>
       </c>
     </row>
+    <row r="3067">
+      <c r="A3067" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B3067" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3067" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D3067" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3067" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3067"/>
+  <dimension ref="A1:E3068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83225,6 +83225,33 @@
         </is>
       </c>
     </row>
+    <row r="3068">
+      <c r="A3068" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B3068" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3068" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D3068" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3068" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3068"/>
+  <dimension ref="A1:E3069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83252,6 +83252,33 @@
         </is>
       </c>
     </row>
+    <row r="3069">
+      <c r="A3069" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B3069" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3069" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D3069" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3069" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3069"/>
+  <dimension ref="A1:E3070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83279,6 +83279,33 @@
         </is>
       </c>
     </row>
+    <row r="3070">
+      <c r="A3070" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B3070" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3070" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D3070" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E3070" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3070"/>
+  <dimension ref="A1:E3071"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83306,6 +83306,33 @@
         </is>
       </c>
     </row>
+    <row r="3071">
+      <c r="A3071" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B3071" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3071" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D3071" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E3071" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3071"/>
+  <dimension ref="A1:E3072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83333,6 +83333,33 @@
         </is>
       </c>
     </row>
+    <row r="3072">
+      <c r="A3072" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B3072" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3072" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3072" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3072" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3072"/>
+  <dimension ref="A1:E3073"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83360,6 +83360,33 @@
         </is>
       </c>
     </row>
+    <row r="3073">
+      <c r="A3073" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B3073" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3073" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3073" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3073" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3073"/>
+  <dimension ref="A1:E3075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83387,6 +83387,60 @@
         </is>
       </c>
     </row>
+    <row r="3074">
+      <c r="A3074" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B3074" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3074" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3074" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3074" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3075">
+      <c r="A3075" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B3075" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3075" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D3075" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3075" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3075"/>
+  <dimension ref="A1:E3076"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83441,6 +83441,33 @@
         </is>
       </c>
     </row>
+    <row r="3076">
+      <c r="A3076" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B3076" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3076" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3076" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3076" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3076"/>
+  <dimension ref="A1:E3077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83468,6 +83468,33 @@
         </is>
       </c>
     </row>
+    <row r="3077">
+      <c r="A3077" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B3077" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3077" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D3077" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3077" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3077"/>
+  <dimension ref="A1:E3078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83495,6 +83495,33 @@
         </is>
       </c>
     </row>
+    <row r="3078">
+      <c r="A3078" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B3078" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3078" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D3078" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3078" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3297"/>
+  <dimension ref="A1:E3298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89435,6 +89435,33 @@
         </is>
       </c>
     </row>
+    <row r="3298">
+      <c r="A3298" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B3298" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3298" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D3298" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3298" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3298"/>
+  <dimension ref="A1:E3299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89462,6 +89462,33 @@
         </is>
       </c>
     </row>
+    <row r="3299">
+      <c r="A3299" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3299" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3299" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3299" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3299" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3476"/>
+  <dimension ref="A1:E3479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94268,6 +94268,87 @@
         </is>
       </c>
     </row>
+    <row r="3477">
+      <c r="A3477" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B3477" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3477" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3477" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E3477" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="3478">
+      <c r="A3478" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B3478" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3478" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D3478" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3478" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="3479">
+      <c r="A3479" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B3479" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3479" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D3479" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E3479" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3736"/>
+  <dimension ref="A1:E3737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101288,6 +101288,33 @@
         </is>
       </c>
     </row>
+    <row r="3737">
+      <c r="A3737" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B3737" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3737" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D3737" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E3737" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3737"/>
+  <dimension ref="A1:E3738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101315,6 +101315,33 @@
         </is>
       </c>
     </row>
+    <row r="3738">
+      <c r="A3738" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B3738" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3738" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D3738" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E3738" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3744"/>
+  <dimension ref="A1:E3745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101504,6 +101504,33 @@
         </is>
       </c>
     </row>
+    <row r="3745">
+      <c r="A3745" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3745" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3745" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D3745" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E3745" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3745"/>
+  <dimension ref="A1:E3746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -101531,6 +101531,33 @@
         </is>
       </c>
     </row>
+    <row r="3746">
+      <c r="A3746" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B3746" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3746" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3746" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3746" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3836"/>
+  <dimension ref="A1:E3837"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103988,6 +103988,33 @@
         </is>
       </c>
     </row>
+    <row r="3837">
+      <c r="A3837" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B3837" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3837" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3837" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E3837" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3837"/>
+  <dimension ref="A1:E3838"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104015,6 +104015,33 @@
         </is>
       </c>
     </row>
+    <row r="3838">
+      <c r="A3838" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B3838" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3838" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3838" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3838" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3868"/>
+  <dimension ref="A1:E3871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104852,6 +104852,87 @@
         </is>
       </c>
     </row>
+    <row r="3869">
+      <c r="A3869" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B3869" t="inlineStr">
+        <is>
+          <t>Anguila 9PM</t>
+        </is>
+      </c>
+      <c r="C3869" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D3869" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3869" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
+    <row r="3870">
+      <c r="A3870" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B3870" t="inlineStr">
+        <is>
+          <t>Anguila 10AM</t>
+        </is>
+      </c>
+      <c r="C3870" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3870" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E3870" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="3871">
+      <c r="A3871" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B3871" t="inlineStr">
+        <is>
+          <t>Anguila 1PM</t>
+        </is>
+      </c>
+      <c r="C3871" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D3871" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3871" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/Anguilla history.xlsx
+++ b/data/histories/Anguilla history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3871"/>
+  <dimension ref="A1:E3872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -104933,6 +104933,33 @@
         </is>
       </c>
     </row>
+    <row r="3872">
+      <c r="A3872" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B3872" t="inlineStr">
+        <is>
+          <t>Anguila 6PM</t>
+        </is>
+      </c>
+      <c r="C3872" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3872" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3872" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
